--- a/shopee_man_655.xlsx
+++ b/shopee_man_655.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\StudiKasus_BI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D13059-59C1-46FD-9F21-1FCF0C76A77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B16E400-F43C-4DA6-A7B3-A021AB3E0771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2523,6 +2523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M656"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2536,7 +2537,8 @@
     <col min="8" max="8" width="24.3984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.3984375" customWidth="1"/>
     <col min="10" max="10" width="6.5" customWidth="1"/>
-    <col min="11" max="12" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5" customWidth="1"/>
+    <col min="12" max="12" width="12.59765625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="39.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2622,7 +2624,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2663,7 +2665,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2745,7 +2747,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2942,7 +2944,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3065,7 +3067,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3188,7 +3190,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3227,7 +3229,7 @@
       </c>
       <c r="M17" s="4"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3268,7 +3270,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3307,7 +3309,7 @@
       </c>
       <c r="M19" s="4"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3467,7 +3469,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3508,7 +3510,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3547,7 +3549,7 @@
       </c>
       <c r="M25" s="4"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3586,7 +3588,7 @@
       </c>
       <c r="M26" s="4"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3625,7 +3627,7 @@
       </c>
       <c r="M27" s="4"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3666,7 +3668,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3703,7 +3705,7 @@
       </c>
       <c r="M29" s="4"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3785,7 +3787,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3908,7 +3910,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3945,7 +3947,7 @@
       </c>
       <c r="M35" s="4"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3982,7 +3984,7 @@
       </c>
       <c r="M36" s="4"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4060,7 +4062,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4177,7 +4179,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4216,7 +4218,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -4296,7 +4298,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -4458,7 +4460,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -4495,7 +4497,7 @@
       </c>
       <c r="M49" s="4"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4534,7 +4536,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -4616,7 +4618,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4657,7 +4659,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4778,7 +4780,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4817,7 +4819,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4856,7 +4858,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -5018,7 +5020,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -5098,7 +5100,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -5219,7 +5221,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -5379,7 +5381,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -5418,7 +5420,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -5498,7 +5500,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -5539,7 +5541,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -5699,7 +5701,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5738,7 +5740,7 @@
       </c>
       <c r="M80" s="4"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5777,7 +5779,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5898,7 +5900,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -5939,7 +5941,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -6101,7 +6103,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -6140,7 +6142,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -6222,7 +6224,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -6263,7 +6265,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -6382,7 +6384,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -6421,7 +6423,7 @@
       </c>
       <c r="M97" s="4"/>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -6620,7 +6622,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -6700,7 +6702,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
@@ -6864,7 +6866,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
@@ -6946,7 +6948,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
@@ -6987,7 +6989,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>111</v>
       </c>
@@ -7028,7 +7030,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
@@ -7069,7 +7071,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
@@ -7110,7 +7112,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
@@ -7354,7 +7356,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
@@ -7436,7 +7438,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>122</v>
       </c>
@@ -7557,7 +7559,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>125</v>
       </c>
@@ -7635,7 +7637,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>127</v>
       </c>
@@ -7674,7 +7676,7 @@
       </c>
       <c r="M128" s="4"/>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>128</v>
       </c>
@@ -7754,7 +7756,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>130</v>
       </c>
@@ -7836,7 +7838,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>132</v>
       </c>
@@ -7877,7 +7879,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>133</v>
       </c>
@@ -8115,7 +8117,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>139</v>
       </c>
@@ -8156,7 +8158,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>140</v>
       </c>
@@ -8392,7 +8394,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>146</v>
       </c>
@@ -8433,7 +8435,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>147</v>
       </c>
@@ -8511,7 +8513,7 @@
       </c>
       <c r="M149" s="4"/>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>149</v>
       </c>
@@ -8550,7 +8552,7 @@
       </c>
       <c r="M150" s="4"/>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>150</v>
       </c>
@@ -8589,7 +8591,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>151</v>
       </c>
@@ -8630,7 +8632,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>152</v>
       </c>
@@ -8669,7 +8671,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>153</v>
       </c>
@@ -8710,7 +8712,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>154</v>
       </c>
@@ -8751,7 +8753,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>155</v>
       </c>
@@ -8790,7 +8792,7 @@
       </c>
       <c r="M156" s="4"/>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>156</v>
       </c>
@@ -8868,7 +8870,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>158</v>
       </c>
@@ -8950,7 +8952,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>160</v>
       </c>
@@ -9073,7 +9075,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>163</v>
       </c>
@@ -9235,7 +9237,7 @@
       </c>
       <c r="M167" s="4"/>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>167</v>
       </c>
@@ -9315,7 +9317,7 @@
       </c>
       <c r="M169" s="4"/>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>169</v>
       </c>
@@ -9354,7 +9356,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>170</v>
       </c>
@@ -9512,7 +9514,7 @@
       </c>
       <c r="M174" s="4"/>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>174</v>
       </c>
@@ -9553,7 +9555,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>175</v>
       </c>
@@ -9590,7 +9592,7 @@
       </c>
       <c r="M176" s="4"/>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>176</v>
       </c>
@@ -9668,7 +9670,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>178</v>
       </c>
@@ -9826,7 +9828,7 @@
       </c>
       <c r="M182" s="4"/>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>182</v>
       </c>
@@ -9863,7 +9865,7 @@
       </c>
       <c r="M183" s="4"/>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>183</v>
       </c>
@@ -9900,7 +9902,7 @@
       </c>
       <c r="M184" s="4"/>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>184</v>
       </c>
@@ -9937,7 +9939,7 @@
       </c>
       <c r="M185" s="4"/>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>185</v>
       </c>
@@ -9978,7 +9980,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>186</v>
       </c>
@@ -10017,7 +10019,7 @@
       </c>
       <c r="M187" s="4"/>
     </row>
-    <row r="188" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:13" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>187</v>
       </c>
@@ -10171,7 +10173,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>191</v>
       </c>
@@ -10376,7 +10378,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>196</v>
       </c>
@@ -10456,7 +10458,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>198</v>
       </c>
@@ -10534,7 +10536,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>200</v>
       </c>
@@ -10698,7 +10700,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>204</v>
       </c>
@@ -10776,7 +10778,7 @@
       </c>
       <c r="M206" s="4"/>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>206</v>
       </c>
@@ -10975,7 +10977,7 @@
       </c>
       <c r="M211" s="4"/>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>211</v>
       </c>
@@ -11014,7 +11016,7 @@
       </c>
       <c r="M212" s="4"/>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>212</v>
       </c>
@@ -11053,7 +11055,7 @@
       </c>
       <c r="M213" s="4"/>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>213</v>
       </c>
@@ -11133,7 +11135,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>215</v>
       </c>
@@ -11172,7 +11174,7 @@
       </c>
       <c r="M216" s="4"/>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>216</v>
       </c>
@@ -11213,7 +11215,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>217</v>
       </c>
@@ -11293,7 +11295,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>219</v>
       </c>
@@ -11332,7 +11334,7 @@
       </c>
       <c r="M220" s="4"/>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>220</v>
       </c>
@@ -11492,7 +11494,7 @@
       </c>
       <c r="M224" s="4"/>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>224</v>
       </c>
@@ -11533,7 +11535,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>225</v>
       </c>
@@ -11693,7 +11695,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>229</v>
       </c>
@@ -11732,7 +11734,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>230</v>
       </c>
@@ -11814,7 +11816,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>232</v>
       </c>
@@ -11896,7 +11898,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>234</v>
       </c>
@@ -11976,7 +11978,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>236</v>
       </c>
@@ -12132,7 +12134,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>240</v>
       </c>
@@ -12173,7 +12175,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>241</v>
       </c>
@@ -12253,7 +12255,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>243</v>
       </c>
@@ -12370,7 +12372,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>246</v>
       </c>
@@ -12409,7 +12411,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>247</v>
       </c>
@@ -12571,7 +12573,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>251</v>
       </c>
@@ -12608,7 +12610,7 @@
       </c>
       <c r="M252" s="4"/>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>252</v>
       </c>
@@ -12686,7 +12688,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>254</v>
       </c>
@@ -12766,7 +12768,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>256</v>
       </c>
@@ -12969,7 +12971,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>261</v>
       </c>
@@ -13088,7 +13090,7 @@
       </c>
       <c r="M264" s="4"/>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>264</v>
       </c>
@@ -13127,7 +13129,7 @@
       </c>
       <c r="M265" s="4"/>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>265</v>
       </c>
@@ -13531,7 +13533,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>275</v>
       </c>
@@ -13613,7 +13615,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>277</v>
       </c>
@@ -13654,7 +13656,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>278</v>
       </c>
@@ -13732,7 +13734,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>280</v>
       </c>
@@ -14009,7 +14011,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>287</v>
       </c>
@@ -14048,7 +14050,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>288</v>
       </c>
@@ -14085,7 +14087,7 @@
       </c>
       <c r="M289" s="4"/>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>289</v>
       </c>
@@ -14126,7 +14128,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>290</v>
       </c>
@@ -14165,7 +14167,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>291</v>
       </c>
@@ -14204,7 +14206,7 @@
       </c>
       <c r="M292" s="4"/>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>292</v>
       </c>
@@ -14368,7 +14370,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>296</v>
       </c>
@@ -14487,7 +14489,7 @@
       </c>
       <c r="M299" s="4"/>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>299</v>
       </c>
@@ -14608,7 +14610,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>302</v>
       </c>
@@ -14649,7 +14651,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>303</v>
       </c>
@@ -14727,7 +14729,7 @@
       </c>
       <c r="M305" s="4"/>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>305</v>
       </c>
@@ -14766,7 +14768,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>306</v>
       </c>
@@ -14846,7 +14848,7 @@
       </c>
       <c r="M308" s="4"/>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>308</v>
       </c>
@@ -15049,7 +15051,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>313</v>
       </c>
@@ -15090,7 +15092,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>314</v>
       </c>
@@ -15289,7 +15291,7 @@
       </c>
       <c r="M319" s="4"/>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>319</v>
       </c>
@@ -15328,7 +15330,7 @@
       </c>
       <c r="M320" s="4"/>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>320</v>
       </c>
@@ -15406,7 +15408,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>322</v>
       </c>
@@ -15447,7 +15449,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>323</v>
       </c>
@@ -15488,7 +15490,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>324</v>
       </c>
@@ -15529,7 +15531,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>325</v>
       </c>
@@ -15652,7 +15654,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>328</v>
       </c>
@@ -15771,7 +15773,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>331</v>
       </c>
@@ -15810,7 +15812,7 @@
       </c>
       <c r="M332" s="4"/>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>332</v>
       </c>
@@ -15851,7 +15853,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>333</v>
       </c>
@@ -15890,7 +15892,7 @@
       </c>
       <c r="M334" s="4"/>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>334</v>
       </c>
@@ -15929,7 +15931,7 @@
       </c>
       <c r="M335" s="4"/>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>335</v>
       </c>
@@ -15970,7 +15972,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>336</v>
       </c>
@@ -16052,7 +16054,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>338</v>
       </c>
@@ -16091,7 +16093,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>339</v>
       </c>
@@ -16130,7 +16132,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>340</v>
       </c>
@@ -16208,7 +16210,7 @@
       </c>
       <c r="M342" s="4"/>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>342</v>
       </c>
@@ -16370,7 +16372,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>346</v>
       </c>
@@ -16450,7 +16452,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>348</v>
       </c>
@@ -16487,7 +16489,7 @@
       </c>
       <c r="M349" s="4"/>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>349</v>
       </c>
@@ -16526,7 +16528,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>350</v>
       </c>
@@ -16608,7 +16610,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>352</v>
       </c>
@@ -16688,7 +16690,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>354</v>
       </c>
@@ -16848,7 +16850,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>358</v>
       </c>
@@ -16887,7 +16889,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>359</v>
       </c>
@@ -16967,7 +16969,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>361</v>
       </c>
@@ -17049,7 +17051,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>363</v>
       </c>
@@ -17088,7 +17090,7 @@
       </c>
       <c r="M364" s="4"/>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>364</v>
       </c>
@@ -17129,7 +17131,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>365</v>
       </c>
@@ -17207,7 +17209,7 @@
       </c>
       <c r="M367" s="4"/>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>367</v>
       </c>
@@ -17248,7 +17250,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>368</v>
       </c>
@@ -17330,7 +17332,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>370</v>
       </c>
@@ -17369,7 +17371,7 @@
       </c>
       <c r="M371" s="4"/>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>371</v>
       </c>
@@ -17570,7 +17572,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>376</v>
       </c>
@@ -17726,7 +17728,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>380</v>
       </c>
@@ -17767,7 +17769,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>381</v>
       </c>
@@ -17808,7 +17810,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>382</v>
       </c>
@@ -17849,7 +17851,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>383</v>
       </c>
@@ -17890,7 +17892,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>384</v>
       </c>
@@ -18052,7 +18054,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>388</v>
       </c>
@@ -18130,7 +18132,7 @@
       </c>
       <c r="M390" s="4"/>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>390</v>
       </c>
@@ -18169,7 +18171,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>391</v>
       </c>
@@ -18210,7 +18212,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>392</v>
       </c>
@@ -18290,7 +18292,7 @@
       </c>
       <c r="M394" s="4"/>
     </row>
-    <row r="395" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:13" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>394</v>
       </c>
@@ -18370,7 +18372,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>396</v>
       </c>
@@ -18409,7 +18411,7 @@
       </c>
       <c r="M397" s="4"/>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>397</v>
       </c>
@@ -18448,7 +18450,7 @@
       </c>
       <c r="M398" s="4"/>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>398</v>
       </c>
@@ -18487,7 +18489,7 @@
       </c>
       <c r="M399" s="4"/>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>399</v>
       </c>
@@ -18528,7 +18530,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>400</v>
       </c>
@@ -18567,7 +18569,7 @@
       </c>
       <c r="M401" s="4"/>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>401</v>
       </c>
@@ -18684,7 +18686,7 @@
       </c>
       <c r="M404" s="4"/>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>404</v>
       </c>
@@ -18723,7 +18725,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>405</v>
       </c>
@@ -18762,7 +18764,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>406</v>
       </c>
@@ -18965,7 +18967,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>411</v>
       </c>
@@ -19045,7 +19047,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>413</v>
       </c>
@@ -19086,7 +19088,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>414</v>
       </c>
@@ -19166,7 +19168,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>416</v>
       </c>
@@ -19205,7 +19207,7 @@
       </c>
       <c r="M417" s="4"/>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>417</v>
       </c>
@@ -19246,7 +19248,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>418</v>
       </c>
@@ -19283,7 +19285,7 @@
       </c>
       <c r="M419" s="4"/>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>419</v>
       </c>
@@ -19322,7 +19324,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>420</v>
       </c>
@@ -19566,7 +19568,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>426</v>
       </c>
@@ -19603,7 +19605,7 @@
       </c>
       <c r="M427" s="4"/>
     </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>427</v>
       </c>
@@ -19720,7 +19722,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="431" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>430</v>
       </c>
@@ -19761,7 +19763,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>431</v>
       </c>
@@ -19802,7 +19804,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>432</v>
       </c>
@@ -19999,7 +20001,7 @@
       </c>
       <c r="M437" s="4"/>
     </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>437</v>
       </c>
@@ -20157,7 +20159,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="442" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>441</v>
       </c>
@@ -20313,7 +20315,7 @@
       </c>
       <c r="M445" s="4"/>
     </row>
-    <row r="446" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>445</v>
       </c>
@@ -20354,7 +20356,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>446</v>
       </c>
@@ -20391,7 +20393,7 @@
       </c>
       <c r="M447" s="4"/>
     </row>
-    <row r="448" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>447</v>
       </c>
@@ -20596,7 +20598,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>452</v>
       </c>
@@ -20637,7 +20639,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>453</v>
       </c>
@@ -20678,7 +20680,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>454</v>
       </c>
@@ -20719,7 +20721,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>455</v>
       </c>
@@ -20756,7 +20758,7 @@
       </c>
       <c r="M456" s="4"/>
     </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>456</v>
       </c>
@@ -20877,7 +20879,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>459</v>
       </c>
@@ -20955,7 +20957,7 @@
       </c>
       <c r="M461" s="4"/>
     </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>461</v>
       </c>
@@ -21158,7 +21160,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="467" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467">
         <v>466</v>
       </c>
@@ -21277,7 +21279,7 @@
       </c>
       <c r="M469" s="4"/>
     </row>
-    <row r="470" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>469</v>
       </c>
@@ -21441,7 +21443,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="474" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>473</v>
       </c>
@@ -21482,7 +21484,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="475" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>474</v>
       </c>
@@ -21638,7 +21640,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="479" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>478</v>
       </c>
@@ -21677,7 +21679,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="480" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>479</v>
       </c>
@@ -21714,7 +21716,7 @@
       </c>
       <c r="M480" s="4"/>
     </row>
-    <row r="481" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>480</v>
       </c>
@@ -21753,7 +21755,7 @@
       </c>
       <c r="M481" s="4"/>
     </row>
-    <row r="482" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>481</v>
       </c>
@@ -21790,7 +21792,7 @@
       </c>
       <c r="M482" s="4"/>
     </row>
-    <row r="483" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>482</v>
       </c>
@@ -21952,7 +21954,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="487" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>486</v>
       </c>
@@ -22030,7 +22032,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="489" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>488</v>
       </c>
@@ -22069,7 +22071,7 @@
       </c>
       <c r="M489" s="4"/>
     </row>
-    <row r="490" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>489</v>
       </c>
@@ -22268,7 +22270,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="495" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>494</v>
       </c>
@@ -22508,7 +22510,7 @@
       </c>
       <c r="M500" s="4"/>
     </row>
-    <row r="501" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>500</v>
       </c>
@@ -22588,7 +22590,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="503" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503">
         <v>502</v>
       </c>
@@ -22627,7 +22629,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="504" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504">
         <v>503</v>
       </c>
@@ -22664,7 +22666,7 @@
       </c>
       <c r="M504" s="4"/>
     </row>
-    <row r="505" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>504</v>
       </c>
@@ -22746,7 +22748,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="507" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>506</v>
       </c>
@@ -22785,7 +22787,7 @@
       </c>
       <c r="M507" s="4"/>
     </row>
-    <row r="508" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>507</v>
       </c>
@@ -22863,7 +22865,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="510" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>509</v>
       </c>
@@ -22943,7 +22945,7 @@
       </c>
       <c r="M511" s="4"/>
     </row>
-    <row r="512" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>511</v>
       </c>
@@ -23023,7 +23025,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="514" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>513</v>
       </c>
@@ -23220,7 +23222,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="519" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>518</v>
       </c>
@@ -23259,7 +23261,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="520" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>519</v>
       </c>
@@ -23300,7 +23302,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="521" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>520</v>
       </c>
@@ -23378,7 +23380,7 @@
       </c>
       <c r="M522" s="4"/>
     </row>
-    <row r="523" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>522</v>
       </c>
@@ -23417,7 +23419,7 @@
       </c>
       <c r="M523" s="4"/>
     </row>
-    <row r="524" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>523</v>
       </c>
@@ -23456,7 +23458,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="525" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>524</v>
       </c>
@@ -23538,7 +23540,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="527" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>526</v>
       </c>
@@ -23618,7 +23620,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="529" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529">
         <v>528</v>
       </c>
@@ -23823,7 +23825,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="534" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534">
         <v>533</v>
       </c>
@@ -23862,7 +23864,7 @@
       </c>
       <c r="M534" s="4"/>
     </row>
-    <row r="535" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535">
         <v>534</v>
       </c>
@@ -23903,7 +23905,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="536" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536">
         <v>535</v>
       </c>
@@ -24061,7 +24063,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="540" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540">
         <v>539</v>
       </c>
@@ -24182,7 +24184,7 @@
       </c>
       <c r="M542" s="4"/>
     </row>
-    <row r="543" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543">
         <v>542</v>
       </c>
@@ -24221,7 +24223,7 @@
       </c>
       <c r="M543" s="4"/>
     </row>
-    <row r="544" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544">
         <v>543</v>
       </c>
@@ -24262,7 +24264,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="545" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545">
         <v>544</v>
       </c>
@@ -24344,7 +24346,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="547" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547">
         <v>546</v>
       </c>
@@ -24385,7 +24387,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="548" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548">
         <v>547</v>
       </c>
@@ -24621,7 +24623,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="554" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554">
         <v>553</v>
       </c>
@@ -24662,7 +24664,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="555" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>554</v>
       </c>
@@ -24783,7 +24785,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="558" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558">
         <v>557</v>
       </c>
@@ -24822,7 +24824,7 @@
       </c>
       <c r="M558" s="4"/>
     </row>
-    <row r="559" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559">
         <v>558</v>
       </c>
@@ -24902,7 +24904,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="561" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561">
         <v>560</v>
       </c>
@@ -25503,7 +25505,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="576" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576">
         <v>575</v>
       </c>
@@ -25542,7 +25544,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="577" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577">
         <v>576</v>
       </c>
@@ -25583,7 +25585,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="578" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578">
         <v>577</v>
       </c>
@@ -25624,7 +25626,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="579" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579">
         <v>578</v>
       </c>
@@ -25665,7 +25667,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="580" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580">
         <v>579</v>
       </c>
@@ -25706,7 +25708,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="581" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581">
         <v>580</v>
       </c>
@@ -25745,7 +25747,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="582" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582">
         <v>581</v>
       </c>
@@ -25784,7 +25786,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="583" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583">
         <v>582</v>
       </c>
@@ -25981,7 +25983,7 @@
       </c>
       <c r="M587" s="4"/>
     </row>
-    <row r="588" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588">
         <v>587</v>
       </c>
@@ -26020,7 +26022,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="589" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589">
         <v>588</v>
       </c>
@@ -26057,7 +26059,7 @@
       </c>
       <c r="M589" s="4"/>
     </row>
-    <row r="590" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590">
         <v>589</v>
       </c>
@@ -26096,7 +26098,7 @@
       </c>
       <c r="M590" s="4"/>
     </row>
-    <row r="591" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591">
         <v>590</v>
       </c>
@@ -26215,7 +26217,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="594" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594">
         <v>593</v>
       </c>
@@ -26293,7 +26295,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="596" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596">
         <v>595</v>
       </c>
@@ -26332,7 +26334,7 @@
       </c>
       <c r="M596" s="4"/>
     </row>
-    <row r="597" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597">
         <v>596</v>
       </c>
@@ -26371,7 +26373,7 @@
       </c>
       <c r="M597" s="4"/>
     </row>
-    <row r="598" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598">
         <v>597</v>
       </c>
@@ -26410,7 +26412,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="599" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599">
         <v>598</v>
       </c>
@@ -26490,7 +26492,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="601" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601">
         <v>600</v>
       </c>
@@ -26531,7 +26533,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="602" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602">
         <v>601</v>
       </c>
@@ -26570,7 +26572,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="603" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603">
         <v>602</v>
       </c>
@@ -26691,7 +26693,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="606" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606">
         <v>605</v>
       </c>
@@ -26935,7 +26937,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="612" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612">
         <v>611</v>
       </c>
@@ -26974,7 +26976,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="613" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613">
         <v>612</v>
       </c>
@@ -27054,7 +27056,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="615" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615">
         <v>614</v>
       </c>
@@ -27095,7 +27097,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="616" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616">
         <v>615</v>
       </c>
@@ -27298,7 +27300,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="621" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621">
         <v>620</v>
       </c>
@@ -27339,7 +27341,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="622" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622">
         <v>621</v>
       </c>
@@ -27415,7 +27417,7 @@
       </c>
       <c r="M623" s="4"/>
     </row>
-    <row r="624" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624">
         <v>623</v>
       </c>
@@ -27454,7 +27456,7 @@
       </c>
       <c r="M624" s="4"/>
     </row>
-    <row r="625" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625">
         <v>624</v>
       </c>
@@ -27493,7 +27495,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="626" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626">
         <v>625</v>
       </c>
@@ -27573,7 +27575,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="628" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628">
         <v>627</v>
       </c>
@@ -27653,7 +27655,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="630" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630">
         <v>629</v>
       </c>
@@ -27813,7 +27815,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="634" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634">
         <v>633</v>
       </c>
@@ -27893,7 +27895,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="636" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636">
         <v>635</v>
       </c>
@@ -27932,7 +27934,7 @@
       </c>
       <c r="M636" s="4"/>
     </row>
-    <row r="637" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637">
         <v>636</v>
       </c>
@@ -27971,7 +27973,7 @@
       </c>
       <c r="M637" s="4"/>
     </row>
-    <row r="638" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638">
         <v>637</v>
       </c>
@@ -28008,7 +28010,7 @@
       </c>
       <c r="M638" s="4"/>
     </row>
-    <row r="639" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639">
         <v>638</v>
       </c>
@@ -28211,7 +28213,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="644" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644">
         <v>643</v>
       </c>
@@ -28248,7 +28250,7 @@
       </c>
       <c r="M644" s="4"/>
     </row>
-    <row r="645" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645">
         <v>644</v>
       </c>
@@ -28289,7 +28291,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="646" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646">
         <v>645</v>
       </c>
@@ -28330,7 +28332,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="647" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647">
         <v>646</v>
       </c>
@@ -28408,7 +28410,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="649" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649">
         <v>648</v>
       </c>
@@ -28449,7 +28451,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="650" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650">
         <v>649</v>
       </c>
@@ -28527,7 +28529,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="652" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A652">
         <v>651</v>
       </c>
@@ -28603,7 +28605,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="654" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654">
         <v>653</v>
       </c>
@@ -28642,7 +28644,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="655" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655">
         <v>654</v>
       </c>
@@ -28725,6 +28727,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M656" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="Jawa Barat"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:B656">
     <sortCondition ref="B2:B656"/>
   </sortState>
